--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_98_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_98_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
         <v>13</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,10 +821,10 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -904,12 +904,12 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
@@ -1335,7 +1335,7 @@
         <v>8</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1531,10 +1531,10 @@
         <v>15</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1727,10 +1727,10 @@
         <v>14</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2125,10 +2125,10 @@
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X21" t="n">
         <v>6</v>
@@ -2315,10 +2315,10 @@
         <v>26</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -3827,16 +3827,16 @@
         <v>102</v>
       </c>
       <c r="T30" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X30" t="n">
         <v>24</v>
@@ -4295,7 +4295,7 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V35" t="n">
         <v>0</v>
@@ -4880,7 +4880,7 @@
         <v>8</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -5076,10 +5076,10 @@
         <v>-2</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V39" t="n">
         <v>0</v>
@@ -5471,7 +5471,7 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V41" t="n">
         <v>0</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -6059,7 +6059,7 @@
         <v>0</v>
       </c>
       <c r="U44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V44" t="n">
         <v>0</v>
@@ -6392,10 +6392,10 @@
         <v>78</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="V46" t="n">
         <v>0</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_98_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_98_EL.xlsx
@@ -674,10 +674,10 @@
         <v>13</v>
       </c>
       <c r="N2" t="n">
+        <v>14</v>
+      </c>
+      <c r="O2" t="n">
         <v>24</v>
-      </c>
-      <c r="O2" t="n">
-        <v>34</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -692,20 +692,20 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>58.33</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>75.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>47.62</t>
+          <t>45.00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>15</v>
       </c>
       <c r="N3" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="O3" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="P3" t="n">
         <v>2</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>78.95</t>
+          <t>57.89</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.16</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1347,14 +1347,14 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA17" t="n">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2327,14 +2327,14 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y22" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AA22" t="n">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
@@ -2371,14 +2371,14 @@
         </is>
       </c>
       <c r="AJ22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>40.0%</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3839,14 +3839,14 @@
         <v>2</v>
       </c>
       <c r="X30" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y30" t="n">
         <v>24</v>
       </c>
-      <c r="Y30" t="n">
-        <v>34</v>
-      </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK30" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5088,14 +5088,14 @@
         <v>0</v>
       </c>
       <c r="X39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA39" t="n">
@@ -5480,14 +5480,14 @@
         <v>0</v>
       </c>
       <c r="X41" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y41" t="n">
         <v>4</v>
       </c>
-      <c r="Y41" t="n">
-        <v>6</v>
-      </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -5676,14 +5676,14 @@
         <v>0</v>
       </c>
       <c r="X42" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="Y42" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA42" t="n">
@@ -6068,10 +6068,10 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Y44" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
@@ -6404,14 +6404,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="Y46" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="AA46" t="n">
